--- a/backend/temp/invoices_export.xlsx
+++ b/backend/temp/invoices_export.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line Items" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +423,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,27 +465,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Vendor/Exporter</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Customer/Importer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tax Amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tax %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Total Amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Amount</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fraud Score</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Level</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Created At</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,32 +531,262 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Eurasia Trade Corp (Russia)</t>
-        </is>
+          <t>Polayadi Global Exports Ltd (China)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Polayadi Global Exports Ltd (China)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>266500</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39845</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>306345</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-02-03 09:19:08.872006</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Invoice ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HS Code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tax %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tax Amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tron Ore Fines</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>260111</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>iron_ore</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>287895</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>47500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49875</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Eurasia Trade Corp (Russia)</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hyundai venue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>870321</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>passenger_cars</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>289275</v>
+        <v>15000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>75000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18750</v>
+      </c>
+      <c r="J3" t="n">
+        <v>93750</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Steel rod</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>720851</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>steel_products</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>720</v>
+      </c>
+      <c r="G4" t="n">
+        <v>144000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18720</v>
+      </c>
+      <c r="J4" t="n">
+        <v>162720</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/temp/invoices_export.xlsx
+++ b/backend/temp/invoices_export.xlsx
@@ -430,8 +430,8 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -516,11 +516,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,33 +531,33 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Polayadi Global Exports Ltd (China)</t>
+          <t>Eurasia Trade Corp (Russia)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Polayadi Global Exports Ltd (China)</t>
+          <t>Eurasia Trade Corp (Russia)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>266500</v>
       </c>
       <c r="I2" t="n">
-        <v>39845</v>
+        <v>21395</v>
       </c>
       <c r="J2" t="n">
-        <v>14.95</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>306345</v>
+        <v>287895</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-03 09:19:08.872006</t>
+          <t>2026-03-02 03:51:45.672851</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>russia</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -730,24 +730,24 @@
         <v>75000</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>18750</v>
+        <v>7500</v>
       </c>
       <c r="J3" t="n">
-        <v>93750</v>
+        <v>82500</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>russia</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -775,17 +775,17 @@
         <v>144000</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>18720</v>
+        <v>11520</v>
       </c>
       <c r="J4" t="n">
-        <v>162720</v>
+        <v>155520</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>russia</t>
         </is>
       </c>
     </row>

--- a/backend/temp/invoices_export.xlsx
+++ b/backend/temp/invoices_export.xlsx
@@ -423,14 +423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Vendor/Exporter</t>
+          <t>Exporter (Vendor)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Customer/Importer</t>
+          <t>Importer (Customer)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -520,53 +520,109 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>146989</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Eurasia Trade Corp (Russia)</t>
+          <t>AstraZeneca (UK)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Eurasia Trade Corp (Russia)</t>
+          <t>MSC (INDIA)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>india</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>266500</v>
       </c>
       <c r="I2" t="n">
+        <v>35525</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="K2" t="n">
+        <v>302025</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:42:03.695845</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dragon Global Exports Ltd (China)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Eurasia Trade Corp (Russia)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>266500</v>
+      </c>
+      <c r="I3" t="n">
         <v>21395</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>287895</v>
       </c>
-      <c r="L2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-02 03:51:45.672851</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:42:26.046520</t>
         </is>
       </c>
     </row>
@@ -581,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -657,7 +713,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>146989</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -695,14 +751,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>india</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>146989</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -730,39 +786,39 @@
         <v>75000</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>7500</v>
+        <v>18750</v>
       </c>
       <c r="J3" t="n">
-        <v>82500</v>
+        <v>93750</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>india</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>146989</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Steel rod</t>
+          <t>Panadol tablets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>720851</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steel_products</t>
+          <t>medicines</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -775,15 +831,150 @@
         <v>144000</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J4" t="n">
+        <v>158400</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tron Ore Fines</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>260111</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>iron_ore</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>500</v>
+      </c>
+      <c r="F5" t="n">
+        <v>95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2375</v>
+      </c>
+      <c r="J5" t="n">
+        <v>49875</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hyundai venue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>870321</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>passenger_cars</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>82500</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Steel rod</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>720851</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>steel_products</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>720</v>
+      </c>
+      <c r="G7" t="n">
+        <v>144000</v>
+      </c>
+      <c r="H7" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I7" t="n">
         <v>11520</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J7" t="n">
         <v>155520</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>russia</t>
         </is>
